--- a/data/xlsx_csv/notas.xlsx
+++ b/data/xlsx_csv/notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizan\Desktop\Universidad\Practicas_Bifi\Dashboard_GitHubRepo\unizar_dashboard\data\xlsx_csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409D15B2-C1D3-4AFB-92C7-C6A5F17D4CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15870DF6-9378-4268-BE83-64B1211FE86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -565,6 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -629,7 +630,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -685,7 +686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -741,7 +742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -797,7 +798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -853,7 +854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
@@ -909,7 +910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -965,7 +966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -1021,7 +1022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -1077,7 +1078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1133,7 +1134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -1189,7 +1190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -1245,7 +1246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -1301,7 +1302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -1357,12 +1358,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1">
         <v>26909</v>
@@ -1418,7 +1419,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="1">
         <v>26910</v>
@@ -1469,12 +1470,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1">
         <v>26958</v>
@@ -1525,7 +1526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
@@ -1581,7 +1582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -1637,7 +1638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -1693,7 +1694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
@@ -1749,7 +1750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>18</v>
       </c>
@@ -1805,7 +1806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1861,7 +1862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1917,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>18</v>
       </c>
@@ -1973,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>18</v>
       </c>
@@ -2029,7 +2030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>18</v>
       </c>
@@ -2085,7 +2086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>18</v>
       </c>
@@ -2141,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>18</v>
       </c>
@@ -2197,7 +2198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>18</v>
       </c>
@@ -2253,7 +2254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>18</v>
       </c>
@@ -2309,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>18</v>
       </c>
@@ -2365,7 +2366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>18</v>
       </c>
@@ -2421,7 +2422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>18</v>
       </c>
@@ -2477,7 +2478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>18</v>
       </c>
@@ -2533,7 +2534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>18</v>
       </c>
@@ -2589,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>18</v>
       </c>
@@ -2645,7 +2646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>18</v>
       </c>
@@ -2701,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
@@ -2757,7 +2758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>18</v>
       </c>
@@ -2813,7 +2814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>18</v>
       </c>
@@ -2869,7 +2870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>18</v>
       </c>
@@ -2925,7 +2926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>18</v>
       </c>
@@ -2981,7 +2982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>18</v>
       </c>
@@ -3037,7 +3038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>18</v>
       </c>
@@ -3093,7 +3094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>18</v>
       </c>
@@ -3149,7 +3150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>18</v>
       </c>
@@ -3205,7 +3206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>18</v>
       </c>
@@ -3261,7 +3262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>18</v>
       </c>
@@ -3317,7 +3318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>18</v>
       </c>
@@ -3373,7 +3374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>18</v>
       </c>
@@ -3429,7 +3430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>18</v>
       </c>
@@ -3485,7 +3486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>18</v>
       </c>
@@ -3541,7 +3542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>18</v>
       </c>
@@ -3597,7 +3598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>18</v>
       </c>
@@ -3653,7 +3654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>18</v>
       </c>
@@ -3709,7 +3710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>18</v>
       </c>
@@ -3765,7 +3766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>75</v>
       </c>
@@ -3821,7 +3822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>75</v>
       </c>
@@ -3877,7 +3878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>75</v>
       </c>
@@ -3933,7 +3934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>75</v>
       </c>
@@ -3989,7 +3990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>75</v>
       </c>
@@ -4045,7 +4046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>75</v>
       </c>
@@ -4101,7 +4102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>75</v>
       </c>
@@ -4157,7 +4158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>75</v>
       </c>
@@ -4213,7 +4214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>75</v>
       </c>
@@ -4269,7 +4270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>75</v>
       </c>
@@ -4325,7 +4326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>75</v>
       </c>
@@ -4381,7 +4382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>75</v>
       </c>
@@ -4437,12 +4438,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C70" s="1">
         <v>26909</v>
@@ -4498,7 +4499,7 @@
         <v>75</v>
       </c>
       <c r="B71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71" s="1">
         <v>26910</v>
@@ -4549,12 +4550,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B72" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72" s="1">
         <v>26958</v>
@@ -4605,7 +4606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>75</v>
       </c>
@@ -4661,7 +4662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>75</v>
       </c>
@@ -4717,7 +4718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>75</v>
       </c>
@@ -4773,7 +4774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>75</v>
       </c>
@@ -4829,7 +4830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>75</v>
       </c>
@@ -4885,7 +4886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>75</v>
       </c>
@@ -4941,7 +4942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>75</v>
       </c>
@@ -4997,7 +4998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>75</v>
       </c>
@@ -5053,7 +5054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>75</v>
       </c>
@@ -5109,7 +5110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>75</v>
       </c>
@@ -5165,7 +5166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>75</v>
       </c>
@@ -5221,7 +5222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,7 +5278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>75</v>
       </c>
@@ -5333,7 +5334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5389,7 +5390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>75</v>
       </c>
@@ -5445,7 +5446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>75</v>
       </c>
@@ -5501,7 +5502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>75</v>
       </c>
@@ -5557,7 +5558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>75</v>
       </c>
@@ -5613,7 +5614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>75</v>
       </c>
@@ -5669,7 +5670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>75</v>
       </c>
@@ -5725,7 +5726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>75</v>
       </c>
@@ -5781,7 +5782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>75</v>
       </c>
@@ -5837,7 +5838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>75</v>
       </c>
@@ -5893,7 +5894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>75</v>
       </c>
@@ -5949,7 +5950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>75</v>
       </c>
@@ -6005,7 +6006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>75</v>
       </c>
@@ -6061,7 +6062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,7 +6118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>75</v>
       </c>
@@ -6173,7 +6174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>75</v>
       </c>
@@ -6229,7 +6230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>75</v>
       </c>
@@ -6285,7 +6286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>75</v>
       </c>
@@ -6341,7 +6342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>75</v>
       </c>
@@ -6397,7 +6398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>75</v>
       </c>
@@ -6453,7 +6454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>75</v>
       </c>
@@ -6509,7 +6510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>75</v>
       </c>
@@ -6565,7 +6566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>75</v>
       </c>
@@ -6621,7 +6622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>75</v>
       </c>
@@ -6677,7 +6678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>75</v>
       </c>
@@ -6733,7 +6734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>78</v>
       </c>
@@ -6789,7 +6790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>78</v>
       </c>
@@ -6845,7 +6846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>78</v>
       </c>
@@ -6901,7 +6902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>78</v>
       </c>
@@ -6957,7 +6958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>78</v>
       </c>
@@ -7013,7 +7014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>78</v>
       </c>
@@ -7069,7 +7070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>78</v>
       </c>
@@ -7125,7 +7126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>78</v>
       </c>
@@ -7181,7 +7182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>78</v>
       </c>
@@ -7237,7 +7238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>78</v>
       </c>
@@ -7293,12 +7294,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B121" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C121" s="1">
         <v>26909</v>
@@ -7354,7 +7355,7 @@
         <v>78</v>
       </c>
       <c r="B122" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C122" s="1">
         <v>26910</v>
@@ -7405,12 +7406,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B123" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C123" s="1">
         <v>26958</v>
@@ -7461,7 +7462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>78</v>
       </c>
@@ -7517,7 +7518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>78</v>
       </c>
@@ -7573,7 +7574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>78</v>
       </c>
@@ -7629,7 +7630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>78</v>
       </c>
@@ -7685,7 +7686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>78</v>
       </c>
@@ -7741,7 +7742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>78</v>
       </c>
@@ -7797,7 +7798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>78</v>
       </c>
@@ -7853,7 +7854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>78</v>
       </c>
@@ -7909,7 +7910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>78</v>
       </c>
@@ -7965,7 +7966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>78</v>
       </c>
@@ -8021,7 +8022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>78</v>
       </c>
@@ -8077,7 +8078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>78</v>
       </c>
@@ -8133,7 +8134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>78</v>
       </c>
@@ -8189,7 +8190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>78</v>
       </c>
@@ -8245,7 +8246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>78</v>
       </c>
@@ -8301,7 +8302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>78</v>
       </c>
@@ -8357,7 +8358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>78</v>
       </c>
@@ -8413,7 +8414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>78</v>
       </c>
@@ -8469,7 +8470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>78</v>
       </c>
@@ -8525,7 +8526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>78</v>
       </c>
@@ -8581,7 +8582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>78</v>
       </c>
@@ -8637,7 +8638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>78</v>
       </c>
@@ -8693,7 +8694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>78</v>
       </c>
@@ -8749,7 +8750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>78</v>
       </c>
@@ -8805,7 +8806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>78</v>
       </c>
@@ -8861,7 +8862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>78</v>
       </c>
@@ -8917,7 +8918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>78</v>
       </c>
@@ -8973,7 +8974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>78</v>
       </c>
@@ -9029,7 +9030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>78</v>
       </c>
@@ -9085,7 +9086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>78</v>
       </c>
@@ -9141,7 +9142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>78</v>
       </c>
@@ -9197,7 +9198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>78</v>
       </c>
@@ -9253,7 +9254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>78</v>
       </c>
@@ -9309,7 +9310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>78</v>
       </c>
@@ -9365,7 +9366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>78</v>
       </c>
@@ -9421,7 +9422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>78</v>
       </c>
@@ -9477,7 +9478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>78</v>
       </c>
@@ -9533,7 +9534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>78</v>
       </c>
@@ -9589,7 +9590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>78</v>
       </c>
@@ -9645,7 +9646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>78</v>
       </c>
@@ -9701,7 +9702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>79</v>
       </c>
@@ -9757,7 +9758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>79</v>
       </c>
@@ -9813,7 +9814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>79</v>
       </c>
@@ -9869,7 +9870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>79</v>
       </c>
@@ -9925,7 +9926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>79</v>
       </c>
@@ -9981,7 +9982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>79</v>
       </c>
@@ -10037,7 +10038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>79</v>
       </c>
@@ -10093,7 +10094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>79</v>
       </c>
@@ -10149,7 +10150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>79</v>
       </c>
@@ -10205,7 +10206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>79</v>
       </c>
@@ -10261,12 +10262,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B174" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C174" s="1">
         <v>26909</v>
@@ -10322,7 +10323,7 @@
         <v>79</v>
       </c>
       <c r="B175" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C175" s="1">
         <v>26910</v>
@@ -10373,12 +10374,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B176" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C176" s="1">
         <v>26958</v>
@@ -10429,7 +10430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>79</v>
       </c>
@@ -10485,7 +10486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>79</v>
       </c>
@@ -10541,7 +10542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>79</v>
       </c>
@@ -10597,7 +10598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>79</v>
       </c>
@@ -10653,7 +10654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>79</v>
       </c>
@@ -10709,7 +10710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>79</v>
       </c>
@@ -10765,7 +10766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>79</v>
       </c>
@@ -10821,7 +10822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>79</v>
       </c>
@@ -10877,7 +10878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>79</v>
       </c>
@@ -10933,7 +10934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>79</v>
       </c>
@@ -10989,7 +10990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>79</v>
       </c>
@@ -11045,7 +11046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>79</v>
       </c>
@@ -11101,7 +11102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>79</v>
       </c>
@@ -11157,7 +11158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>79</v>
       </c>
@@ -11213,7 +11214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>79</v>
       </c>
@@ -11269,7 +11270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>79</v>
       </c>
@@ -11325,7 +11326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>79</v>
       </c>
@@ -11381,7 +11382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>79</v>
       </c>
@@ -11437,7 +11438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>79</v>
       </c>
@@ -11493,7 +11494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>79</v>
       </c>
@@ -11549,7 +11550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>79</v>
       </c>
@@ -11605,7 +11606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>79</v>
       </c>
@@ -11661,7 +11662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>79</v>
       </c>
@@ -11717,7 +11718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>79</v>
       </c>
@@ -11773,7 +11774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>79</v>
       </c>
@@ -11829,7 +11830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>79</v>
       </c>
@@ -11885,7 +11886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>79</v>
       </c>
@@ -11941,7 +11942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>79</v>
       </c>
@@ -11997,7 +11998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>79</v>
       </c>
@@ -12053,7 +12054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>79</v>
       </c>
@@ -12109,7 +12110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>79</v>
       </c>
@@ -12165,7 +12166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>79</v>
       </c>
@@ -12221,7 +12222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>79</v>
       </c>
@@ -12277,7 +12278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>79</v>
       </c>
@@ -12333,7 +12334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>79</v>
       </c>
@@ -12389,7 +12390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>79</v>
       </c>
@@ -12445,7 +12446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>79</v>
       </c>
@@ -12501,7 +12502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>79</v>
       </c>
@@ -12557,7 +12558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>79</v>
       </c>
@@ -12613,7 +12614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>79</v>
       </c>
@@ -12669,7 +12670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>80</v>
       </c>
@@ -12725,7 +12726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>80</v>
       </c>
@@ -12781,7 +12782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>80</v>
       </c>
@@ -12837,7 +12838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>80</v>
       </c>
@@ -12893,7 +12894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>80</v>
       </c>
@@ -12949,7 +12950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>80</v>
       </c>
@@ -13005,7 +13006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>80</v>
       </c>
@@ -13061,7 +13062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>80</v>
       </c>
@@ -13117,7 +13118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>80</v>
       </c>
@@ -13173,7 +13174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>80</v>
       </c>
@@ -13229,7 +13230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>80</v>
       </c>
@@ -13285,12 +13286,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B228" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C228" s="1">
         <v>26909</v>
@@ -13346,7 +13347,7 @@
         <v>80</v>
       </c>
       <c r="B229" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C229" s="1">
         <v>26910</v>
@@ -13397,12 +13398,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B230" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C230" s="1">
         <v>26958</v>
@@ -13453,7 +13454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>80</v>
       </c>
@@ -13509,7 +13510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>80</v>
       </c>
@@ -13565,7 +13566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>80</v>
       </c>
@@ -13621,7 +13622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>80</v>
       </c>
@@ -13677,7 +13678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>80</v>
       </c>
@@ -13733,7 +13734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>80</v>
       </c>
@@ -13789,7 +13790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>80</v>
       </c>
@@ -13845,7 +13846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>80</v>
       </c>
@@ -13901,7 +13902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>80</v>
       </c>
@@ -13957,7 +13958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>80</v>
       </c>
@@ -14013,7 +14014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>80</v>
       </c>
@@ -14069,7 +14070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>80</v>
       </c>
@@ -14125,7 +14126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>80</v>
       </c>
@@ -14181,7 +14182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>80</v>
       </c>
@@ -14237,7 +14238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>80</v>
       </c>
@@ -14293,7 +14294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>80</v>
       </c>
@@ -14349,7 +14350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>80</v>
       </c>
@@ -14405,7 +14406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>80</v>
       </c>
@@ -14461,7 +14462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>80</v>
       </c>
@@ -14517,7 +14518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>80</v>
       </c>
@@ -14573,7 +14574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>80</v>
       </c>
@@ -14629,7 +14630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>80</v>
       </c>
@@ -14685,7 +14686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>80</v>
       </c>
@@ -14741,7 +14742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>80</v>
       </c>
@@ -14797,7 +14798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>80</v>
       </c>
@@ -14853,7 +14854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>80</v>
       </c>
@@ -14909,7 +14910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>80</v>
       </c>
@@ -14965,7 +14966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>80</v>
       </c>
@@ -15021,7 +15022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>80</v>
       </c>
@@ -15077,7 +15078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>80</v>
       </c>
@@ -15133,7 +15134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>80</v>
       </c>
@@ -15189,7 +15190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>80</v>
       </c>
@@ -15245,7 +15246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>80</v>
       </c>
@@ -15301,7 +15302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>80</v>
       </c>
@@ -15357,7 +15358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>80</v>
       </c>
@@ -15413,7 +15414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>80</v>
       </c>
@@ -15469,7 +15470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>80</v>
       </c>
@@ -15525,7 +15526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>80</v>
       </c>
@@ -15581,7 +15582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>80</v>
       </c>
@@ -15637,7 +15638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>83</v>
       </c>
@@ -15693,7 +15694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>83</v>
       </c>
@@ -15749,7 +15750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>83</v>
       </c>
@@ -15805,7 +15806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>83</v>
       </c>
@@ -15861,7 +15862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>83</v>
       </c>
@@ -15917,7 +15918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>83</v>
       </c>
@@ -15973,7 +15974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>83</v>
       </c>
@@ -16029,7 +16030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>83</v>
       </c>
@@ -16085,7 +16086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>83</v>
       </c>
@@ -16141,7 +16142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>83</v>
       </c>
@@ -16197,12 +16198,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B280" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C280" s="1">
         <v>26909</v>
@@ -16258,7 +16259,7 @@
         <v>83</v>
       </c>
       <c r="B281" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C281" s="1">
         <v>26910</v>
@@ -16309,12 +16310,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B282" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C282" s="1">
         <v>26958</v>
@@ -16365,7 +16366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>83</v>
       </c>
@@ -16421,7 +16422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>83</v>
       </c>
@@ -16477,7 +16478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>83</v>
       </c>
@@ -16533,7 +16534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>83</v>
       </c>
@@ -16589,7 +16590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>83</v>
       </c>
@@ -16645,7 +16646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>83</v>
       </c>
@@ -16701,7 +16702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>83</v>
       </c>
@@ -16757,7 +16758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>83</v>
       </c>
@@ -16813,7 +16814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>83</v>
       </c>
@@ -16869,7 +16870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>83</v>
       </c>
@@ -16925,7 +16926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>83</v>
       </c>
@@ -16981,7 +16982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>83</v>
       </c>
@@ -17037,7 +17038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>83</v>
       </c>
@@ -17093,7 +17094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>83</v>
       </c>
@@ -17149,7 +17150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>83</v>
       </c>
@@ -17205,7 +17206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>83</v>
       </c>
@@ -17261,7 +17262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>83</v>
       </c>
@@ -17317,7 +17318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>83</v>
       </c>
@@ -17373,7 +17374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>83</v>
       </c>
@@ -17429,7 +17430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>83</v>
       </c>
@@ -17485,7 +17486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>83</v>
       </c>
@@ -17541,7 +17542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>83</v>
       </c>
@@ -17597,7 +17598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>83</v>
       </c>
@@ -17653,7 +17654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>83</v>
       </c>
@@ -17709,7 +17710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>83</v>
       </c>
@@ -17765,7 +17766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>83</v>
       </c>
@@ -17821,7 +17822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>83</v>
       </c>
@@ -17877,7 +17878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>83</v>
       </c>
@@ -17933,7 +17934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>83</v>
       </c>
@@ -17989,7 +17990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>83</v>
       </c>
@@ -18045,7 +18046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>83</v>
       </c>
@@ -18101,7 +18102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>83</v>
       </c>
@@ -18157,7 +18158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>83</v>
       </c>
@@ -18213,7 +18214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>83</v>
       </c>
@@ -18269,7 +18270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>83</v>
       </c>
@@ -18325,7 +18326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>83</v>
       </c>
@@ -18381,7 +18382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>83</v>
       </c>
@@ -18437,7 +18438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>83</v>
       </c>
@@ -18493,7 +18494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>83</v>
       </c>
@@ -18549,7 +18550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>84</v>
       </c>
@@ -18605,7 +18606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>84</v>
       </c>
@@ -18661,7 +18662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>84</v>
       </c>
@@ -18717,7 +18718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>84</v>
       </c>
@@ -18773,7 +18774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>84</v>
       </c>
@@ -18829,7 +18830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>84</v>
       </c>
@@ -18885,7 +18886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>84</v>
       </c>
@@ -18941,7 +18942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>84</v>
       </c>
@@ -18997,7 +18998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>84</v>
       </c>
@@ -19053,7 +19054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>84</v>
       </c>
@@ -19109,7 +19110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>84</v>
       </c>
@@ -19165,7 +19166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>84</v>
       </c>
@@ -19221,7 +19222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>84</v>
       </c>
@@ -19277,12 +19278,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B335" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C335" s="1">
         <v>26909</v>
@@ -19338,7 +19339,7 @@
         <v>84</v>
       </c>
       <c r="B336" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C336" s="1">
         <v>26910</v>
@@ -19389,7 +19390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>84</v>
       </c>
@@ -19445,7 +19446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>84</v>
       </c>
@@ -19501,7 +19502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>84</v>
       </c>
@@ -19557,7 +19558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>84</v>
       </c>
@@ -19613,7 +19614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>84</v>
       </c>
@@ -19669,7 +19670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>84</v>
       </c>
@@ -19725,7 +19726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>84</v>
       </c>
@@ -19781,7 +19782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>84</v>
       </c>
@@ -19837,7 +19838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>84</v>
       </c>
@@ -19893,7 +19894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>84</v>
       </c>
@@ -19949,7 +19950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>84</v>
       </c>
@@ -20005,7 +20006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>84</v>
       </c>
@@ -20061,7 +20062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>84</v>
       </c>
@@ -20117,7 +20118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>84</v>
       </c>
@@ -20173,7 +20174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>84</v>
       </c>
@@ -20229,7 +20230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>84</v>
       </c>
@@ -20285,7 +20286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>84</v>
       </c>
@@ -20341,7 +20342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>84</v>
       </c>
@@ -20397,7 +20398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>84</v>
       </c>
@@ -20453,7 +20454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>84</v>
       </c>
@@ -20509,7 +20510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>84</v>
       </c>
@@ -20565,7 +20566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>84</v>
       </c>
@@ -20621,7 +20622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>84</v>
       </c>
@@ -20677,7 +20678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>84</v>
       </c>
@@ -20733,7 +20734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>84</v>
       </c>
@@ -20789,7 +20790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>84</v>
       </c>
@@ -20845,7 +20846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>84</v>
       </c>
@@ -20901,7 +20902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>84</v>
       </c>
@@ -20957,7 +20958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>84</v>
       </c>
@@ -21013,7 +21014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>84</v>
       </c>
@@ -21069,7 +21070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>84</v>
       </c>
@@ -21125,7 +21126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>84</v>
       </c>
@@ -21181,7 +21182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>84</v>
       </c>
@@ -21237,7 +21238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>84</v>
       </c>
@@ -21293,7 +21294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>84</v>
       </c>
@@ -21349,7 +21350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>84</v>
       </c>
@@ -21405,7 +21406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>84</v>
       </c>
@@ -21461,7 +21462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>84</v>
       </c>
@@ -21517,7 +21518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>89</v>
       </c>
@@ -21573,7 +21574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>89</v>
       </c>
@@ -21629,7 +21630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>89</v>
       </c>
@@ -21685,7 +21686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>89</v>
       </c>
@@ -21741,7 +21742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>89</v>
       </c>
@@ -21797,7 +21798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>89</v>
       </c>
@@ -21853,7 +21854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>89</v>
       </c>
@@ -21909,7 +21910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>89</v>
       </c>
@@ -21965,7 +21966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>89</v>
       </c>
@@ -22021,7 +22022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>89</v>
       </c>
@@ -22077,12 +22078,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B385" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C385" s="1">
         <v>26909</v>
@@ -22138,7 +22139,7 @@
         <v>89</v>
       </c>
       <c r="B386" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C386" s="1">
         <v>26910</v>
@@ -22189,7 +22190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>89</v>
       </c>
@@ -22245,7 +22246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>89</v>
       </c>
@@ -22301,7 +22302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>89</v>
       </c>
@@ -22357,7 +22358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>89</v>
       </c>
@@ -22413,7 +22414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>89</v>
       </c>
@@ -22469,7 +22470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>89</v>
       </c>
@@ -22525,7 +22526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>89</v>
       </c>
@@ -22581,7 +22582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>89</v>
       </c>
@@ -22637,7 +22638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>89</v>
       </c>
@@ -22693,7 +22694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>89</v>
       </c>
@@ -22749,7 +22750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>89</v>
       </c>
@@ -22805,7 +22806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>89</v>
       </c>
@@ -22861,7 +22862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>89</v>
       </c>
@@ -22917,7 +22918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>89</v>
       </c>
@@ -22973,7 +22974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>89</v>
       </c>
@@ -23029,7 +23030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>89</v>
       </c>
@@ -23085,7 +23086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>89</v>
       </c>
@@ -23141,7 +23142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>89</v>
       </c>
@@ -23197,7 +23198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>89</v>
       </c>
@@ -23253,7 +23254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>89</v>
       </c>
@@ -23309,7 +23310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>89</v>
       </c>
@@ -23365,7 +23366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>89</v>
       </c>
@@ -23421,7 +23422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>89</v>
       </c>
@@ -23477,7 +23478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>89</v>
       </c>
@@ -23533,7 +23534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>89</v>
       </c>
@@ -23589,7 +23590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>89</v>
       </c>
@@ -23645,7 +23646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>89</v>
       </c>
@@ -23701,7 +23702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>89</v>
       </c>
@@ -23757,7 +23758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>89</v>
       </c>
@@ -23813,7 +23814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>89</v>
       </c>
@@ -23869,7 +23870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>89</v>
       </c>
@@ -23925,7 +23926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>89</v>
       </c>
@@ -23981,7 +23982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>89</v>
       </c>
@@ -24037,7 +24038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>89</v>
       </c>
@@ -24093,7 +24094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>89</v>
       </c>
@@ -24149,7 +24150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>89</v>
       </c>
@@ -24205,7 +24206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>89</v>
       </c>
@@ -24261,7 +24262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>89</v>
       </c>
@@ -24317,7 +24318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>89</v>
       </c>
@@ -24373,7 +24374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>89</v>
       </c>
@@ -24429,7 +24430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>91</v>
       </c>
@@ -24485,7 +24486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>91</v>
       </c>
@@ -24541,7 +24542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>91</v>
       </c>
@@ -24597,7 +24598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>91</v>
       </c>
@@ -24653,7 +24654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>91</v>
       </c>
@@ -24709,7 +24710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>91</v>
       </c>
@@ -24765,7 +24766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>91</v>
       </c>
@@ -24821,7 +24822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>91</v>
       </c>
@@ -24877,7 +24878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>91</v>
       </c>
@@ -24933,12 +24934,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B436" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C436" s="1">
         <v>26909</v>
@@ -24994,7 +24995,7 @@
         <v>91</v>
       </c>
       <c r="B437" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C437" s="1">
         <v>26910</v>
@@ -25045,7 +25046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>91</v>
       </c>
@@ -25101,7 +25102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>91</v>
       </c>
@@ -25157,7 +25158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>91</v>
       </c>
@@ -25213,7 +25214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>91</v>
       </c>
@@ -25269,7 +25270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>91</v>
       </c>
@@ -25325,7 +25326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>91</v>
       </c>
@@ -25381,7 +25382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>91</v>
       </c>
@@ -25437,7 +25438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>91</v>
       </c>
@@ -25493,7 +25494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>91</v>
       </c>
@@ -25549,7 +25550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>91</v>
       </c>
@@ -25605,7 +25606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>91</v>
       </c>
@@ -25661,7 +25662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>91</v>
       </c>
@@ -25717,7 +25718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>91</v>
       </c>
@@ -25773,7 +25774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>91</v>
       </c>
@@ -25829,7 +25830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>91</v>
       </c>
@@ -25885,7 +25886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>91</v>
       </c>
@@ -25941,7 +25942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>91</v>
       </c>
@@ -25997,7 +25998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>91</v>
       </c>
@@ -26053,7 +26054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>91</v>
       </c>
@@ -26109,7 +26110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>91</v>
       </c>
@@ -26165,7 +26166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>91</v>
       </c>
@@ -26221,7 +26222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>91</v>
       </c>
@@ -26277,7 +26278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>91</v>
       </c>
@@ -26333,7 +26334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>91</v>
       </c>
@@ -26389,7 +26390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>91</v>
       </c>
@@ -26445,7 +26446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>91</v>
       </c>
@@ -26501,7 +26502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>91</v>
       </c>
@@ -26557,7 +26558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>91</v>
       </c>
@@ -26613,7 +26614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>91</v>
       </c>
@@ -26669,7 +26670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>91</v>
       </c>
@@ -26725,7 +26726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>91</v>
       </c>
@@ -26781,7 +26782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>91</v>
       </c>
@@ -26837,7 +26838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>91</v>
       </c>
@@ -26893,7 +26894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>91</v>
       </c>
@@ -26949,7 +26950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>91</v>
       </c>
@@ -27005,7 +27006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>91</v>
       </c>
@@ -27061,7 +27062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>91</v>
       </c>
@@ -27117,7 +27118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>91</v>
       </c>
@@ -27173,7 +27174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>91</v>
       </c>
@@ -27229,7 +27230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>92</v>
       </c>
@@ -27285,7 +27286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>92</v>
       </c>
@@ -27341,7 +27342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>92</v>
       </c>
@@ -27397,7 +27398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>92</v>
       </c>
@@ -27453,7 +27454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>92</v>
       </c>
@@ -27509,7 +27510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>92</v>
       </c>
@@ -27565,7 +27566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>92</v>
       </c>
@@ -27621,7 +27622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>92</v>
       </c>
@@ -27677,7 +27678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>92</v>
       </c>
@@ -27733,7 +27734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>92</v>
       </c>
@@ -27789,7 +27790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>92</v>
       </c>
@@ -27845,7 +27846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>92</v>
       </c>
@@ -27901,7 +27902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>92</v>
       </c>
@@ -27957,7 +27958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>92</v>
       </c>
@@ -28013,7 +28014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>92</v>
       </c>
@@ -28069,7 +28070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>92</v>
       </c>
@@ -28125,7 +28126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>92</v>
       </c>
@@ -28181,7 +28182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>92</v>
       </c>
@@ -28237,7 +28238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>92</v>
       </c>
@@ -28293,7 +28294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>92</v>
       </c>
@@ -28349,7 +28350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>92</v>
       </c>
@@ -28405,7 +28406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>92</v>
       </c>
@@ -28461,7 +28462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>92</v>
       </c>
@@ -28517,7 +28518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>92</v>
       </c>
@@ -28573,7 +28574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>92</v>
       </c>
@@ -28629,7 +28630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>92</v>
       </c>
@@ -28685,7 +28686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>92</v>
       </c>
@@ -28741,7 +28742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>92</v>
       </c>
@@ -28797,12 +28798,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B505" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C505" s="1">
         <v>26909</v>
@@ -28858,7 +28859,7 @@
         <v>92</v>
       </c>
       <c r="B506" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C506" s="1">
         <v>26910</v>
@@ -28909,7 +28910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>92</v>
       </c>
@@ -28965,7 +28966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>92</v>
       </c>
@@ -29021,7 +29022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>92</v>
       </c>
@@ -29077,7 +29078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>92</v>
       </c>
@@ -29133,7 +29134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>92</v>
       </c>
@@ -29189,7 +29190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>92</v>
       </c>
@@ -29245,7 +29246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>92</v>
       </c>
@@ -29301,7 +29302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>92</v>
       </c>
@@ -29357,7 +29358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>92</v>
       </c>
@@ -29413,7 +29414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>92</v>
       </c>
@@ -29469,7 +29470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>92</v>
       </c>
@@ -29525,7 +29526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>92</v>
       </c>
@@ -29581,7 +29582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>92</v>
       </c>
@@ -29637,7 +29638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>92</v>
       </c>
@@ -29693,7 +29694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>92</v>
       </c>
@@ -29749,7 +29750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>92</v>
       </c>
@@ -29805,7 +29806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>92</v>
       </c>
@@ -29861,7 +29862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>92</v>
       </c>
@@ -29917,7 +29918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>92</v>
       </c>
@@ -29973,7 +29974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>92</v>
       </c>
@@ -30029,7 +30030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>92</v>
       </c>
@@ -30085,7 +30086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>93</v>
       </c>
@@ -30141,7 +30142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>93</v>
       </c>
@@ -30197,7 +30198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>93</v>
       </c>
@@ -30253,7 +30254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>93</v>
       </c>
@@ -30309,7 +30310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>93</v>
       </c>
@@ -30365,7 +30366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>93</v>
       </c>
@@ -30421,7 +30422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>93</v>
       </c>
@@ -30477,7 +30478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>93</v>
       </c>
@@ -30533,7 +30534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>93</v>
       </c>
@@ -30589,7 +30590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>93</v>
       </c>
@@ -30645,7 +30646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>93</v>
       </c>
@@ -30701,7 +30702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>93</v>
       </c>
@@ -30757,7 +30758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>93</v>
       </c>
@@ -30813,7 +30814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>93</v>
       </c>
@@ -30869,7 +30870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>93</v>
       </c>
@@ -30925,7 +30926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>93</v>
       </c>
@@ -30981,7 +30982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>93</v>
       </c>
@@ -31037,7 +31038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>93</v>
       </c>
@@ -31093,7 +31094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>93</v>
       </c>
@@ -31149,7 +31150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>93</v>
       </c>
@@ -31205,7 +31206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>93</v>
       </c>
@@ -31261,7 +31262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>93</v>
       </c>
@@ -31317,7 +31318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>93</v>
       </c>
@@ -31373,7 +31374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>93</v>
       </c>
@@ -31429,7 +31430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>93</v>
       </c>
@@ -31485,7 +31486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>93</v>
       </c>
@@ -31541,7 +31542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>93</v>
       </c>
@@ -31597,12 +31598,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B555" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C555" s="1">
         <v>26909</v>
@@ -31658,7 +31659,7 @@
         <v>93</v>
       </c>
       <c r="B556" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C556" s="1">
         <v>26910</v>
@@ -31709,7 +31710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>93</v>
       </c>
@@ -31765,7 +31766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>93</v>
       </c>
@@ -31821,7 +31822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>93</v>
       </c>
@@ -31877,7 +31878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>93</v>
       </c>
@@ -31933,7 +31934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>93</v>
       </c>
@@ -31989,7 +31990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>93</v>
       </c>
@@ -32045,7 +32046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>93</v>
       </c>
@@ -32101,7 +32102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>93</v>
       </c>
@@ -32157,7 +32158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>93</v>
       </c>
@@ -32213,7 +32214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>93</v>
       </c>
@@ -32269,7 +32270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>93</v>
       </c>
@@ -32325,7 +32326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>93</v>
       </c>
@@ -32381,7 +32382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>93</v>
       </c>
@@ -32437,7 +32438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>93</v>
       </c>
@@ -32493,7 +32494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>93</v>
       </c>
@@ -32549,7 +32550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>93</v>
       </c>
@@ -32605,7 +32606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>93</v>
       </c>
@@ -32661,7 +32662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>93</v>
       </c>
@@ -32717,7 +32718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>93</v>
       </c>
@@ -32773,7 +32774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>93</v>
       </c>
@@ -32829,7 +32830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>93</v>
       </c>
@@ -32885,7 +32886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>94</v>
       </c>
@@ -32941,7 +32942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>94</v>
       </c>
@@ -32997,7 +32998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>94</v>
       </c>
@@ -33053,7 +33054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>94</v>
       </c>
@@ -33109,7 +33110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>94</v>
       </c>
@@ -33165,7 +33166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>94</v>
       </c>
@@ -33221,7 +33222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>94</v>
       </c>
@@ -33277,7 +33278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>94</v>
       </c>
@@ -33333,7 +33334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>94</v>
       </c>
@@ -33389,7 +33390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>94</v>
       </c>
@@ -33445,7 +33446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>94</v>
       </c>
@@ -33501,7 +33502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>94</v>
       </c>
@@ -33557,7 +33558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="590" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>94</v>
       </c>
@@ -33613,7 +33614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>94</v>
       </c>
@@ -33669,7 +33670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>94</v>
       </c>
@@ -33725,7 +33726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>94</v>
       </c>
@@ -33781,7 +33782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>94</v>
       </c>
@@ -33837,7 +33838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>94</v>
       </c>
@@ -33893,7 +33894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>94</v>
       </c>
@@ -33949,7 +33950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>94</v>
       </c>
@@ -34005,7 +34006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>94</v>
       </c>
@@ -34061,7 +34062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>94</v>
       </c>
@@ -34117,7 +34118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>94</v>
       </c>
@@ -34173,7 +34174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>94</v>
       </c>
@@ -34229,7 +34230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>94</v>
       </c>
@@ -34285,7 +34286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>94</v>
       </c>
@@ -34341,7 +34342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>94</v>
       </c>
@@ -34397,12 +34398,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="605" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B605" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C605" s="1">
         <v>26909</v>
@@ -34458,7 +34459,7 @@
         <v>94</v>
       </c>
       <c r="B606" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C606" s="1">
         <v>26910</v>
@@ -34509,7 +34510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>94</v>
       </c>
@@ -34565,7 +34566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>94</v>
       </c>
@@ -34621,7 +34622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>94</v>
       </c>
@@ -34677,7 +34678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>94</v>
       </c>
@@ -34733,7 +34734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>94</v>
       </c>
@@ -34789,7 +34790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>94</v>
       </c>
@@ -34845,7 +34846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>94</v>
       </c>
@@ -34901,7 +34902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="614" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>94</v>
       </c>
@@ -34957,7 +34958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>94</v>
       </c>
@@ -35013,7 +35014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>94</v>
       </c>
@@ -35069,7 +35070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>94</v>
       </c>
@@ -35125,7 +35126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>94</v>
       </c>
@@ -35181,7 +35182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>94</v>
       </c>
@@ -35237,7 +35238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>94</v>
       </c>
@@ -35293,7 +35294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>94</v>
       </c>
@@ -35349,7 +35350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>94</v>
       </c>
@@ -35405,7 +35406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>94</v>
       </c>
@@ -35461,7 +35462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>94</v>
       </c>
@@ -35517,7 +35518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>94</v>
       </c>
@@ -35573,7 +35574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>94</v>
       </c>
@@ -35629,7 +35630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>94</v>
       </c>
@@ -35685,381 +35686,387 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="D1:D1000" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="D1:D1000" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Geología"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter>

--- a/data/xlsx_csv/notas.xlsx
+++ b/data/xlsx_csv/notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizan\Desktop\Universidad\Practicas_Bifi\Dashboard_GitHubRepo\unizar_dashboard\data\xlsx_csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15870DF6-9378-4268-BE83-64B1211FE86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCC36AB-0A17-4F6A-89CD-D60D97151730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -314,7 +314,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -325,6 +325,18 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -347,9 +359,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,7 +578,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:R1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -630,7 +642,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -686,7 +698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -742,7 +754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -798,7 +810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -854,7 +866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
@@ -910,7 +922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -966,7 +978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -1022,7 +1034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -1078,7 +1090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1134,7 +1146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -1190,7 +1202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -1246,7 +1258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -1302,7 +1314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -1358,7 +1370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -1470,7 +1482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -1526,7 +1538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
@@ -1582,7 +1594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -1638,7 +1650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -1694,7 +1706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
@@ -1750,7 +1762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>18</v>
       </c>
@@ -1806,7 +1818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1862,7 +1874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1918,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>18</v>
       </c>
@@ -1974,7 +1986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>18</v>
       </c>
@@ -2030,7 +2042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>18</v>
       </c>
@@ -2086,7 +2098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>18</v>
       </c>
@@ -2142,7 +2154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>18</v>
       </c>
@@ -2198,7 +2210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>18</v>
       </c>
@@ -2254,7 +2266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>18</v>
       </c>
@@ -2310,7 +2322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>18</v>
       </c>
@@ -2366,7 +2378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>18</v>
       </c>
@@ -2422,7 +2434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>18</v>
       </c>
@@ -2478,7 +2490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>18</v>
       </c>
@@ -2534,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>18</v>
       </c>
@@ -2590,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>18</v>
       </c>
@@ -2646,7 +2658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>18</v>
       </c>
@@ -2702,7 +2714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
@@ -2758,7 +2770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>18</v>
       </c>
@@ -2814,7 +2826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>18</v>
       </c>
@@ -2870,7 +2882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>18</v>
       </c>
@@ -2926,7 +2938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>18</v>
       </c>
@@ -2982,7 +2994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>18</v>
       </c>
@@ -3038,7 +3050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>18</v>
       </c>
@@ -3094,7 +3106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>18</v>
       </c>
@@ -3150,7 +3162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>18</v>
       </c>
@@ -3206,7 +3218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>18</v>
       </c>
@@ -3262,7 +3274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>18</v>
       </c>
@@ -3318,7 +3330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>18</v>
       </c>
@@ -3374,7 +3386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>18</v>
       </c>
@@ -3430,7 +3442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>18</v>
       </c>
@@ -3486,7 +3498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>18</v>
       </c>
@@ -3542,7 +3554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>18</v>
       </c>
@@ -3598,7 +3610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>18</v>
       </c>
@@ -3654,7 +3666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>18</v>
       </c>
@@ -3710,7 +3722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>18</v>
       </c>
@@ -3766,7 +3778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>75</v>
       </c>
@@ -3822,7 +3834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>75</v>
       </c>
@@ -3878,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>75</v>
       </c>
@@ -3934,7 +3946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>75</v>
       </c>
@@ -3990,7 +4002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>75</v>
       </c>
@@ -4046,7 +4058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>75</v>
       </c>
@@ -4102,7 +4114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>75</v>
       </c>
@@ -4158,7 +4170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>75</v>
       </c>
@@ -4214,7 +4226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>75</v>
       </c>
@@ -4270,7 +4282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>75</v>
       </c>
@@ -4326,7 +4338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>75</v>
       </c>
@@ -4382,7 +4394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>75</v>
       </c>
@@ -4438,7 +4450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>75</v>
       </c>
@@ -4550,7 +4562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>75</v>
       </c>
@@ -4606,7 +4618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>75</v>
       </c>
@@ -4662,7 +4674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>75</v>
       </c>
@@ -4718,7 +4730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>75</v>
       </c>
@@ -4774,7 +4786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>75</v>
       </c>
@@ -4830,7 +4842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>75</v>
       </c>
@@ -4886,7 +4898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>75</v>
       </c>
@@ -4942,7 +4954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>75</v>
       </c>
@@ -4998,7 +5010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>75</v>
       </c>
@@ -5054,7 +5066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>75</v>
       </c>
@@ -5110,7 +5122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>75</v>
       </c>
@@ -5166,7 +5178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>75</v>
       </c>
@@ -5222,7 +5234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>75</v>
       </c>
@@ -5278,7 +5290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>75</v>
       </c>
@@ -5334,7 +5346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5390,7 +5402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>75</v>
       </c>
@@ -5446,7 +5458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>75</v>
       </c>
@@ -5502,7 +5514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>75</v>
       </c>
@@ -5558,7 +5570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>75</v>
       </c>
@@ -5614,7 +5626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>75</v>
       </c>
@@ -5670,7 +5682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>75</v>
       </c>
@@ -5726,7 +5738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>75</v>
       </c>
@@ -5782,7 +5794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>75</v>
       </c>
@@ -5838,7 +5850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>75</v>
       </c>
@@ -5894,7 +5906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>75</v>
       </c>
@@ -5950,7 +5962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>75</v>
       </c>
@@ -6006,7 +6018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>75</v>
       </c>
@@ -6062,7 +6074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,7 +6130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>75</v>
       </c>
@@ -6174,7 +6186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>75</v>
       </c>
@@ -6230,7 +6242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>75</v>
       </c>
@@ -6286,7 +6298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>75</v>
       </c>
@@ -6342,7 +6354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>75</v>
       </c>
@@ -6398,7 +6410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>75</v>
       </c>
@@ -6454,7 +6466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>75</v>
       </c>
@@ -6510,7 +6522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>75</v>
       </c>
@@ -6566,7 +6578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>75</v>
       </c>
@@ -6622,7 +6634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>75</v>
       </c>
@@ -6678,7 +6690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>75</v>
       </c>
@@ -6734,7 +6746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>78</v>
       </c>
@@ -6790,7 +6802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>78</v>
       </c>
@@ -6846,7 +6858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>78</v>
       </c>
@@ -6902,7 +6914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>78</v>
       </c>
@@ -6958,7 +6970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>78</v>
       </c>
@@ -7014,7 +7026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>78</v>
       </c>
@@ -7070,7 +7082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>78</v>
       </c>
@@ -7126,7 +7138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>78</v>
       </c>
@@ -7182,7 +7194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>78</v>
       </c>
@@ -7238,7 +7250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>78</v>
       </c>
@@ -7294,7 +7306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>78</v>
       </c>
@@ -7406,7 +7418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>78</v>
       </c>
@@ -7462,7 +7474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>78</v>
       </c>
@@ -7518,7 +7530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>78</v>
       </c>
@@ -7574,7 +7586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>78</v>
       </c>
@@ -7630,7 +7642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>78</v>
       </c>
@@ -7686,7 +7698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>78</v>
       </c>
@@ -7742,7 +7754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>78</v>
       </c>
@@ -7798,7 +7810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>78</v>
       </c>
@@ -7854,7 +7866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>78</v>
       </c>
@@ -7910,7 +7922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>78</v>
       </c>
@@ -7966,7 +7978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>78</v>
       </c>
@@ -8022,7 +8034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>78</v>
       </c>
@@ -8078,7 +8090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>78</v>
       </c>
@@ -8134,7 +8146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>78</v>
       </c>
@@ -8190,7 +8202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>78</v>
       </c>
@@ -8246,7 +8258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>78</v>
       </c>
@@ -8302,7 +8314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>78</v>
       </c>
@@ -8358,7 +8370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>78</v>
       </c>
@@ -8414,7 +8426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>78</v>
       </c>
@@ -8470,7 +8482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>78</v>
       </c>
@@ -8526,7 +8538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>78</v>
       </c>
@@ -8582,7 +8594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>78</v>
       </c>
@@ -8638,7 +8650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>78</v>
       </c>
@@ -8694,7 +8706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>78</v>
       </c>
@@ -8750,7 +8762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>78</v>
       </c>
@@ -8806,7 +8818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>78</v>
       </c>
@@ -8862,7 +8874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>78</v>
       </c>
@@ -8918,7 +8930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>78</v>
       </c>
@@ -8974,7 +8986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>78</v>
       </c>
@@ -9030,7 +9042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>78</v>
       </c>
@@ -9086,7 +9098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>78</v>
       </c>
@@ -9142,7 +9154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>78</v>
       </c>
@@ -9198,7 +9210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>78</v>
       </c>
@@ -9254,7 +9266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>78</v>
       </c>
@@ -9310,7 +9322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>78</v>
       </c>
@@ -9366,7 +9378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>78</v>
       </c>
@@ -9422,7 +9434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>78</v>
       </c>
@@ -9478,7 +9490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>78</v>
       </c>
@@ -9534,7 +9546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>78</v>
       </c>
@@ -9590,7 +9602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>78</v>
       </c>
@@ -9646,7 +9658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>78</v>
       </c>
@@ -9702,7 +9714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>79</v>
       </c>
@@ -9758,7 +9770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>79</v>
       </c>
@@ -9814,7 +9826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>79</v>
       </c>
@@ -9870,7 +9882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>79</v>
       </c>
@@ -9926,7 +9938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>79</v>
       </c>
@@ -9982,7 +9994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>79</v>
       </c>
@@ -10038,7 +10050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>79</v>
       </c>
@@ -10094,7 +10106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>79</v>
       </c>
@@ -10150,7 +10162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>79</v>
       </c>
@@ -10206,7 +10218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>79</v>
       </c>
@@ -10262,7 +10274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>79</v>
       </c>
@@ -10374,7 +10386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>79</v>
       </c>
@@ -10430,7 +10442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>79</v>
       </c>
@@ -10486,7 +10498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>79</v>
       </c>
@@ -10542,7 +10554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>79</v>
       </c>
@@ -10598,7 +10610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>79</v>
       </c>
@@ -10654,7 +10666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>79</v>
       </c>
@@ -10710,7 +10722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>79</v>
       </c>
@@ -10766,7 +10778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>79</v>
       </c>
@@ -10822,7 +10834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>79</v>
       </c>
@@ -10878,7 +10890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>79</v>
       </c>
@@ -10934,7 +10946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>79</v>
       </c>
@@ -10990,7 +11002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>79</v>
       </c>
@@ -11046,7 +11058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>79</v>
       </c>
@@ -11102,7 +11114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>79</v>
       </c>
@@ -11158,7 +11170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>79</v>
       </c>
@@ -11214,7 +11226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>79</v>
       </c>
@@ -11270,7 +11282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>79</v>
       </c>
@@ -11326,7 +11338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>79</v>
       </c>
@@ -11382,7 +11394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>79</v>
       </c>
@@ -11438,7 +11450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>79</v>
       </c>
@@ -11494,7 +11506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>79</v>
       </c>
@@ -11550,7 +11562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>79</v>
       </c>
@@ -11606,7 +11618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>79</v>
       </c>
@@ -11662,7 +11674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>79</v>
       </c>
@@ -11718,7 +11730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>79</v>
       </c>
@@ -11774,7 +11786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>79</v>
       </c>
@@ -11830,7 +11842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>79</v>
       </c>
@@ -11886,7 +11898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>79</v>
       </c>
@@ -11942,7 +11954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>79</v>
       </c>
@@ -11998,7 +12010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>79</v>
       </c>
@@ -12054,7 +12066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>79</v>
       </c>
@@ -12110,7 +12122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>79</v>
       </c>
@@ -12166,7 +12178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>79</v>
       </c>
@@ -12222,7 +12234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>79</v>
       </c>
@@ -12278,7 +12290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>79</v>
       </c>
@@ -12334,7 +12346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>79</v>
       </c>
@@ -12390,7 +12402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>79</v>
       </c>
@@ -12446,7 +12458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>79</v>
       </c>
@@ -12502,7 +12514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>79</v>
       </c>
@@ -12558,7 +12570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>79</v>
       </c>
@@ -12614,7 +12626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>79</v>
       </c>
@@ -12670,7 +12682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>80</v>
       </c>
@@ -12726,7 +12738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>80</v>
       </c>
@@ -12782,7 +12794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>80</v>
       </c>
@@ -12838,7 +12850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>80</v>
       </c>
@@ -12894,7 +12906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>80</v>
       </c>
@@ -12950,7 +12962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>80</v>
       </c>
@@ -13006,7 +13018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>80</v>
       </c>
@@ -13062,7 +13074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>80</v>
       </c>
@@ -13118,7 +13130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>80</v>
       </c>
@@ -13174,7 +13186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>80</v>
       </c>
@@ -13230,7 +13242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>80</v>
       </c>
@@ -13286,7 +13298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>80</v>
       </c>
@@ -13398,7 +13410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>80</v>
       </c>
@@ -13454,7 +13466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>80</v>
       </c>
@@ -13510,7 +13522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>80</v>
       </c>
@@ -13566,7 +13578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>80</v>
       </c>
@@ -13622,7 +13634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>80</v>
       </c>
@@ -13678,7 +13690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>80</v>
       </c>
@@ -13734,7 +13746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>80</v>
       </c>
@@ -13790,7 +13802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>80</v>
       </c>
@@ -13846,7 +13858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>80</v>
       </c>
@@ -13902,7 +13914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>80</v>
       </c>
@@ -13958,7 +13970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>80</v>
       </c>
@@ -14014,7 +14026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>80</v>
       </c>
@@ -14070,7 +14082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>80</v>
       </c>
@@ -14126,7 +14138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>80</v>
       </c>
@@ -14182,7 +14194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>80</v>
       </c>
@@ -14238,7 +14250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>80</v>
       </c>
@@ -14294,7 +14306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>80</v>
       </c>
@@ -14350,7 +14362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>80</v>
       </c>
@@ -14406,7 +14418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>80</v>
       </c>
@@ -14462,7 +14474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>80</v>
       </c>
@@ -14518,7 +14530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>80</v>
       </c>
@@ -14574,7 +14586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>80</v>
       </c>
@@ -14630,7 +14642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>80</v>
       </c>
@@ -14686,7 +14698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>80</v>
       </c>
@@ -14742,7 +14754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>80</v>
       </c>
@@ -14798,7 +14810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>80</v>
       </c>
@@ -14854,7 +14866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>80</v>
       </c>
@@ -14910,7 +14922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>80</v>
       </c>
@@ -14966,7 +14978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>80</v>
       </c>
@@ -15022,7 +15034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>80</v>
       </c>
@@ -15078,7 +15090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>80</v>
       </c>
@@ -15134,7 +15146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>80</v>
       </c>
@@ -15190,7 +15202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>80</v>
       </c>
@@ -15246,7 +15258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>80</v>
       </c>
@@ -15302,7 +15314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>80</v>
       </c>
@@ -15358,7 +15370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>80</v>
       </c>
@@ -15414,7 +15426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>80</v>
       </c>
@@ -15470,7 +15482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>80</v>
       </c>
@@ -15526,7 +15538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>80</v>
       </c>
@@ -15582,7 +15594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>80</v>
       </c>
@@ -15638,7 +15650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>83</v>
       </c>
@@ -15694,7 +15706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>83</v>
       </c>
@@ -15750,7 +15762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>83</v>
       </c>
@@ -15806,7 +15818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>83</v>
       </c>
@@ -15862,7 +15874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>83</v>
       </c>
@@ -15918,7 +15930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>83</v>
       </c>
@@ -15974,7 +15986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>83</v>
       </c>
@@ -16030,7 +16042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>83</v>
       </c>
@@ -16086,7 +16098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>83</v>
       </c>
@@ -16142,7 +16154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>83</v>
       </c>
@@ -16198,7 +16210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>83</v>
       </c>
@@ -16310,7 +16322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>83</v>
       </c>
@@ -16366,7 +16378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>83</v>
       </c>
@@ -16422,7 +16434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>83</v>
       </c>
@@ -16478,7 +16490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>83</v>
       </c>
@@ -16534,7 +16546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>83</v>
       </c>
@@ -16590,7 +16602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>83</v>
       </c>
@@ -16646,7 +16658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>83</v>
       </c>
@@ -16702,7 +16714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>83</v>
       </c>
@@ -16758,7 +16770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>83</v>
       </c>
@@ -16814,7 +16826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>83</v>
       </c>
@@ -16870,7 +16882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>83</v>
       </c>
@@ -16926,7 +16938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>83</v>
       </c>
@@ -16982,7 +16994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>83</v>
       </c>
@@ -17038,7 +17050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>83</v>
       </c>
@@ -17094,7 +17106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>83</v>
       </c>
@@ -17150,7 +17162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>83</v>
       </c>
@@ -17206,7 +17218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>83</v>
       </c>
@@ -17262,7 +17274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>83</v>
       </c>
@@ -17318,7 +17330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>83</v>
       </c>
@@ -17374,7 +17386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>83</v>
       </c>
@@ -17430,7 +17442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>83</v>
       </c>
@@ -17486,7 +17498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>83</v>
       </c>
@@ -17542,7 +17554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>83</v>
       </c>
@@ -17598,7 +17610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>83</v>
       </c>
@@ -17654,7 +17666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>83</v>
       </c>
@@ -17710,7 +17722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>83</v>
       </c>
@@ -17766,7 +17778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>83</v>
       </c>
@@ -17822,7 +17834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>83</v>
       </c>
@@ -17878,7 +17890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>83</v>
       </c>
@@ -17934,7 +17946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>83</v>
       </c>
@@ -17990,7 +18002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>83</v>
       </c>
@@ -18046,7 +18058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>83</v>
       </c>
@@ -18102,7 +18114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>83</v>
       </c>
@@ -18158,7 +18170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>83</v>
       </c>
@@ -18214,7 +18226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>83</v>
       </c>
@@ -18270,7 +18282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>83</v>
       </c>
@@ -18326,7 +18338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>83</v>
       </c>
@@ -18382,7 +18394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>83</v>
       </c>
@@ -18438,7 +18450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>83</v>
       </c>
@@ -18494,7 +18506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>83</v>
       </c>
@@ -18550,7 +18562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>84</v>
       </c>
@@ -18606,7 +18618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>84</v>
       </c>
@@ -18662,7 +18674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>84</v>
       </c>
@@ -18718,7 +18730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>84</v>
       </c>
@@ -18774,7 +18786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>84</v>
       </c>
@@ -18830,7 +18842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>84</v>
       </c>
@@ -18886,7 +18898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>84</v>
       </c>
@@ -18942,7 +18954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>84</v>
       </c>
@@ -18998,7 +19010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>84</v>
       </c>
@@ -19054,7 +19066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>84</v>
       </c>
@@ -19110,7 +19122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>84</v>
       </c>
@@ -19166,7 +19178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>84</v>
       </c>
@@ -19222,7 +19234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>84</v>
       </c>
@@ -19278,7 +19290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>84</v>
       </c>
@@ -19390,7 +19402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>84</v>
       </c>
@@ -19446,7 +19458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>84</v>
       </c>
@@ -19502,7 +19514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>84</v>
       </c>
@@ -19558,7 +19570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>84</v>
       </c>
@@ -19614,7 +19626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>84</v>
       </c>
@@ -19670,7 +19682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>84</v>
       </c>
@@ -19726,7 +19738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>84</v>
       </c>
@@ -19782,7 +19794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>84</v>
       </c>
@@ -19838,7 +19850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>84</v>
       </c>
@@ -19894,7 +19906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>84</v>
       </c>
@@ -19950,7 +19962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>84</v>
       </c>
@@ -20006,7 +20018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>84</v>
       </c>
@@ -20062,7 +20074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>84</v>
       </c>
@@ -20118,7 +20130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>84</v>
       </c>
@@ -20174,7 +20186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>84</v>
       </c>
@@ -20230,7 +20242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>84</v>
       </c>
@@ -20286,7 +20298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>84</v>
       </c>
@@ -20342,7 +20354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>84</v>
       </c>
@@ -20398,7 +20410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>84</v>
       </c>
@@ -20454,7 +20466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>84</v>
       </c>
@@ -20510,7 +20522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>84</v>
       </c>
@@ -20566,7 +20578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>84</v>
       </c>
@@ -20622,7 +20634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>84</v>
       </c>
@@ -20678,7 +20690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>84</v>
       </c>
@@ -20734,7 +20746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>84</v>
       </c>
@@ -20790,7 +20802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>84</v>
       </c>
@@ -20846,7 +20858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>84</v>
       </c>
@@ -20902,7 +20914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>84</v>
       </c>
@@ -20958,7 +20970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>84</v>
       </c>
@@ -21014,7 +21026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>84</v>
       </c>
@@ -21070,7 +21082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>84</v>
       </c>
@@ -21126,7 +21138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>84</v>
       </c>
@@ -21182,7 +21194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>84</v>
       </c>
@@ -21238,7 +21250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>84</v>
       </c>
@@ -21294,7 +21306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>84</v>
       </c>
@@ -21350,7 +21362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>84</v>
       </c>
@@ -21406,7 +21418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>84</v>
       </c>
@@ -21462,7 +21474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>84</v>
       </c>
@@ -21518,7 +21530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>89</v>
       </c>
@@ -21574,7 +21586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>89</v>
       </c>
@@ -21630,7 +21642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>89</v>
       </c>
@@ -21686,7 +21698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>89</v>
       </c>
@@ -21742,7 +21754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>89</v>
       </c>
@@ -21798,7 +21810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>89</v>
       </c>
@@ -21854,7 +21866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>89</v>
       </c>
@@ -21910,7 +21922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>89</v>
       </c>
@@ -21966,7 +21978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>89</v>
       </c>
@@ -22022,7 +22034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>89</v>
       </c>
@@ -22078,7 +22090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>89</v>
       </c>
@@ -22190,7 +22202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>89</v>
       </c>
@@ -22246,7 +22258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>89</v>
       </c>
@@ -22302,7 +22314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>89</v>
       </c>
@@ -22358,7 +22370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>89</v>
       </c>
@@ -22414,7 +22426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>89</v>
       </c>
@@ -22470,7 +22482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>89</v>
       </c>
@@ -22526,7 +22538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>89</v>
       </c>
@@ -22582,7 +22594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>89</v>
       </c>
@@ -22638,7 +22650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>89</v>
       </c>
@@ -22694,7 +22706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>89</v>
       </c>
@@ -22750,7 +22762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>89</v>
       </c>
@@ -22806,7 +22818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>89</v>
       </c>
@@ -22862,7 +22874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>89</v>
       </c>
@@ -22918,7 +22930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>89</v>
       </c>
@@ -22974,7 +22986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>89</v>
       </c>
@@ -23030,7 +23042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>89</v>
       </c>
@@ -23086,7 +23098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>89</v>
       </c>
@@ -23142,7 +23154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>89</v>
       </c>
@@ -23198,7 +23210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>89</v>
       </c>
@@ -23254,7 +23266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>89</v>
       </c>
@@ -23310,7 +23322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>89</v>
       </c>
@@ -23366,7 +23378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>89</v>
       </c>
@@ -23422,7 +23434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>89</v>
       </c>
@@ -23478,7 +23490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>89</v>
       </c>
@@ -23534,7 +23546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>89</v>
       </c>
@@ -23590,7 +23602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>89</v>
       </c>
@@ -23646,7 +23658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>89</v>
       </c>
@@ -23702,7 +23714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>89</v>
       </c>
@@ -23758,7 +23770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>89</v>
       </c>
@@ -23814,7 +23826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>89</v>
       </c>
@@ -23870,7 +23882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>89</v>
       </c>
@@ -23926,7 +23938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>89</v>
       </c>
@@ -23982,7 +23994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>89</v>
       </c>
@@ -24038,7 +24050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>89</v>
       </c>
@@ -24094,7 +24106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>89</v>
       </c>
@@ -24150,7 +24162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>89</v>
       </c>
@@ -24206,7 +24218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>89</v>
       </c>
@@ -24262,7 +24274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>89</v>
       </c>
@@ -24318,7 +24330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>89</v>
       </c>
@@ -24374,7 +24386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>89</v>
       </c>
@@ -24430,7 +24442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>91</v>
       </c>
@@ -24486,7 +24498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>91</v>
       </c>
@@ -24542,7 +24554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>91</v>
       </c>
@@ -24598,7 +24610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>91</v>
       </c>
@@ -24654,7 +24666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>91</v>
       </c>
@@ -24710,7 +24722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>91</v>
       </c>
@@ -24766,7 +24778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>91</v>
       </c>
@@ -24822,7 +24834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>91</v>
       </c>
@@ -24878,7 +24890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>91</v>
       </c>
@@ -24934,7 +24946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>91</v>
       </c>
@@ -25046,7 +25058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>91</v>
       </c>
@@ -25102,7 +25114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>91</v>
       </c>
@@ -25158,7 +25170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>91</v>
       </c>
@@ -25214,7 +25226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>91</v>
       </c>
@@ -25270,7 +25282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>91</v>
       </c>
@@ -25326,7 +25338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>91</v>
       </c>
@@ -25382,7 +25394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>91</v>
       </c>
@@ -25438,7 +25450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>91</v>
       </c>
@@ -25494,7 +25506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>91</v>
       </c>
@@ -25550,7 +25562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>91</v>
       </c>
@@ -25606,7 +25618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>91</v>
       </c>
@@ -25662,7 +25674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>91</v>
       </c>
@@ -25718,7 +25730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>91</v>
       </c>
@@ -25774,7 +25786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>91</v>
       </c>
@@ -25830,7 +25842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>91</v>
       </c>
@@ -25886,7 +25898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>91</v>
       </c>
@@ -25942,7 +25954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>91</v>
       </c>
@@ -25998,7 +26010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>91</v>
       </c>
@@ -26054,7 +26066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>91</v>
       </c>
@@ -26110,7 +26122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>91</v>
       </c>
@@ -26166,7 +26178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>91</v>
       </c>
@@ -26222,7 +26234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>91</v>
       </c>
@@ -26278,7 +26290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>91</v>
       </c>
@@ -26334,7 +26346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>91</v>
       </c>
@@ -26390,7 +26402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>91</v>
       </c>
@@ -26446,7 +26458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>91</v>
       </c>
@@ -26502,7 +26514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>91</v>
       </c>
@@ -26558,7 +26570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>91</v>
       </c>
@@ -26614,7 +26626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>91</v>
       </c>
@@ -26670,7 +26682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>91</v>
       </c>
@@ -26726,7 +26738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>91</v>
       </c>
@@ -26782,7 +26794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>91</v>
       </c>
@@ -26838,7 +26850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>91</v>
       </c>
@@ -26894,7 +26906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>91</v>
       </c>
@@ -26950,7 +26962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>91</v>
       </c>
@@ -27006,7 +27018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>91</v>
       </c>
@@ -27062,7 +27074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>91</v>
       </c>
@@ -27118,7 +27130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>91</v>
       </c>
@@ -27174,7 +27186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>91</v>
       </c>
@@ -27230,7 +27242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>92</v>
       </c>
@@ -27286,7 +27298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>92</v>
       </c>
@@ -27342,7 +27354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>92</v>
       </c>
@@ -27398,7 +27410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>92</v>
       </c>
@@ -27454,7 +27466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>92</v>
       </c>
@@ -27510,7 +27522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>92</v>
       </c>
@@ -27566,7 +27578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>92</v>
       </c>
@@ -27622,7 +27634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>92</v>
       </c>
@@ -27678,7 +27690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>92</v>
       </c>
@@ -27734,7 +27746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>92</v>
       </c>
@@ -27790,7 +27802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>92</v>
       </c>
@@ -27846,7 +27858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>92</v>
       </c>
@@ -27902,7 +27914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>92</v>
       </c>
@@ -27958,7 +27970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>92</v>
       </c>
@@ -28014,7 +28026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>92</v>
       </c>
@@ -28070,7 +28082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>92</v>
       </c>
@@ -28126,7 +28138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>92</v>
       </c>
@@ -28182,7 +28194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>92</v>
       </c>
@@ -28238,7 +28250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>92</v>
       </c>
@@ -28294,7 +28306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>92</v>
       </c>
@@ -28350,7 +28362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>92</v>
       </c>
@@ -28406,7 +28418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>92</v>
       </c>
@@ -28462,7 +28474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>92</v>
       </c>
@@ -28518,7 +28530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>92</v>
       </c>
@@ -28574,7 +28586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>92</v>
       </c>
@@ -28630,7 +28642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>92</v>
       </c>
@@ -28686,7 +28698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>92</v>
       </c>
@@ -28742,7 +28754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>92</v>
       </c>
@@ -28798,7 +28810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>92</v>
       </c>
@@ -28910,7 +28922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>92</v>
       </c>
@@ -28966,7 +28978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>92</v>
       </c>
@@ -29022,7 +29034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>92</v>
       </c>
@@ -29078,7 +29090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>92</v>
       </c>
@@ -29134,7 +29146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>92</v>
       </c>
@@ -29190,7 +29202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>92</v>
       </c>
@@ -29246,7 +29258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>92</v>
       </c>
@@ -29302,7 +29314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>92</v>
       </c>
@@ -29358,7 +29370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>92</v>
       </c>
@@ -29414,7 +29426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>92</v>
       </c>
@@ -29470,7 +29482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>92</v>
       </c>
@@ -29526,7 +29538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>92</v>
       </c>
@@ -29582,7 +29594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>92</v>
       </c>
@@ -29638,7 +29650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>92</v>
       </c>
@@ -29694,7 +29706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>92</v>
       </c>
@@ -29750,7 +29762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>92</v>
       </c>
@@ -29806,7 +29818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>92</v>
       </c>
@@ -29862,7 +29874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>92</v>
       </c>
@@ -29918,7 +29930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>92</v>
       </c>
@@ -29974,7 +29986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>92</v>
       </c>
@@ -30030,7 +30042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>92</v>
       </c>
@@ -30086,7 +30098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>93</v>
       </c>
@@ -30142,7 +30154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>93</v>
       </c>
@@ -30198,7 +30210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>93</v>
       </c>
@@ -30254,7 +30266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>93</v>
       </c>
@@ -30310,7 +30322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>93</v>
       </c>
@@ -30366,7 +30378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>93</v>
       </c>
@@ -30422,7 +30434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>93</v>
       </c>
@@ -30478,7 +30490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>93</v>
       </c>
@@ -30534,7 +30546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>93</v>
       </c>
@@ -30590,7 +30602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>93</v>
       </c>
@@ -30646,7 +30658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>93</v>
       </c>
@@ -30702,7 +30714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>93</v>
       </c>
@@ -30758,7 +30770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>93</v>
       </c>
@@ -30814,7 +30826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>93</v>
       </c>
@@ -30870,7 +30882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>93</v>
       </c>
@@ -30926,7 +30938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>93</v>
       </c>
@@ -30982,7 +30994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>93</v>
       </c>
@@ -31038,7 +31050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>93</v>
       </c>
@@ -31094,7 +31106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>93</v>
       </c>
@@ -31150,7 +31162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>93</v>
       </c>
@@ -31206,7 +31218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>93</v>
       </c>
@@ -31262,7 +31274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>93</v>
       </c>
@@ -31318,7 +31330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>93</v>
       </c>
@@ -31374,7 +31386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>93</v>
       </c>
@@ -31430,7 +31442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>93</v>
       </c>
@@ -31486,7 +31498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>93</v>
       </c>
@@ -31542,7 +31554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>93</v>
       </c>
@@ -31598,7 +31610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>93</v>
       </c>
@@ -31710,7 +31722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>93</v>
       </c>
@@ -31766,7 +31778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>93</v>
       </c>
@@ -31822,7 +31834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>93</v>
       </c>
@@ -31878,7 +31890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>93</v>
       </c>
@@ -31934,7 +31946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>93</v>
       </c>
@@ -31990,7 +32002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>93</v>
       </c>
@@ -32046,7 +32058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>93</v>
       </c>
@@ -32102,7 +32114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>93</v>
       </c>
@@ -32158,7 +32170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>93</v>
       </c>
@@ -32214,7 +32226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>93</v>
       </c>
@@ -32270,7 +32282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>93</v>
       </c>
@@ -32326,7 +32338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>93</v>
       </c>
@@ -32382,7 +32394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>93</v>
       </c>
@@ -32438,7 +32450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>93</v>
       </c>
@@ -32494,7 +32506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>93</v>
       </c>
@@ -32550,7 +32562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>93</v>
       </c>
@@ -32606,7 +32618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>93</v>
       </c>
@@ -32662,7 +32674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>93</v>
       </c>
@@ -32718,7 +32730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>93</v>
       </c>
@@ -32774,7 +32786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>93</v>
       </c>
@@ -32830,7 +32842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>93</v>
       </c>
@@ -32886,7 +32898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>94</v>
       </c>
@@ -32942,7 +32954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>94</v>
       </c>
@@ -32998,7 +33010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>94</v>
       </c>
@@ -33054,7 +33066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>94</v>
       </c>
@@ -33110,7 +33122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>94</v>
       </c>
@@ -33166,7 +33178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>94</v>
       </c>
@@ -33222,7 +33234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>94</v>
       </c>
@@ -33278,7 +33290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>94</v>
       </c>
@@ -33334,7 +33346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>94</v>
       </c>
@@ -33390,7 +33402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>94</v>
       </c>
@@ -33446,7 +33458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>94</v>
       </c>
@@ -33502,7 +33514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>94</v>
       </c>
@@ -33558,7 +33570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="590" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>94</v>
       </c>
@@ -33614,7 +33626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>94</v>
       </c>
@@ -33670,7 +33682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>94</v>
       </c>
@@ -33726,7 +33738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>94</v>
       </c>
@@ -33782,7 +33794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>94</v>
       </c>
@@ -33838,7 +33850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>94</v>
       </c>
@@ -33894,7 +33906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>94</v>
       </c>
@@ -33950,7 +33962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>94</v>
       </c>
@@ -34006,7 +34018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>94</v>
       </c>
@@ -34062,7 +34074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>94</v>
       </c>
@@ -34118,7 +34130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>94</v>
       </c>
@@ -34174,7 +34186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>94</v>
       </c>
@@ -34230,7 +34242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>94</v>
       </c>
@@ -34286,7 +34298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>94</v>
       </c>
@@ -34342,7 +34354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>94</v>
       </c>
@@ -34398,7 +34410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="605" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>94</v>
       </c>
@@ -34510,7 +34522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>94</v>
       </c>
@@ -34566,7 +34578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>94</v>
       </c>
@@ -34622,7 +34634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>94</v>
       </c>
@@ -34678,7 +34690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>94</v>
       </c>
@@ -34734,7 +34746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>94</v>
       </c>
@@ -34790,7 +34802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>94</v>
       </c>
@@ -34846,7 +34858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>94</v>
       </c>
@@ -34902,7 +34914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="614" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>94</v>
       </c>
@@ -34958,7 +34970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>94</v>
       </c>
@@ -35014,7 +35026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>94</v>
       </c>
@@ -35070,7 +35082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>94</v>
       </c>
@@ -35126,7 +35138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>94</v>
       </c>
@@ -35182,7 +35194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>94</v>
       </c>
@@ -35238,7 +35250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>94</v>
       </c>
@@ -35294,7 +35306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>94</v>
       </c>
@@ -35350,7 +35362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>94</v>
       </c>
@@ -35406,7 +35418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>94</v>
       </c>
@@ -35462,7 +35474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>94</v>
       </c>
@@ -35518,7 +35530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>94</v>
       </c>
@@ -35574,7 +35586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>94</v>
       </c>
@@ -35630,7 +35642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>94</v>
       </c>
@@ -35686,389 +35698,472 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A628" s="2"/>
+    </row>
+    <row r="629" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A629" s="2"/>
+    </row>
+    <row r="630" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A630" s="2"/>
+    </row>
+    <row r="631" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A631" s="2"/>
+    </row>
+    <row r="632" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A632" s="2"/>
+    </row>
+    <row r="633" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A633" s="2"/>
+    </row>
+    <row r="634" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A634" s="2"/>
+    </row>
+    <row r="635" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A635" s="2"/>
+    </row>
+    <row r="636" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A636" s="2"/>
+    </row>
+    <row r="637" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A637" s="2"/>
+    </row>
+    <row r="638" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A638" s="2"/>
+    </row>
+    <row r="639" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A639" s="2"/>
+    </row>
+    <row r="640" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A640" s="2"/>
+    </row>
+    <row r="641" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A641" s="2"/>
+    </row>
+    <row r="642" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A642" s="2"/>
+    </row>
+    <row r="643" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A643" s="2"/>
+    </row>
+    <row r="644" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A644" s="2"/>
+    </row>
+    <row r="645" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A645" s="2"/>
+    </row>
+    <row r="646" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A646" s="2"/>
+    </row>
+    <row r="647" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A647" s="2"/>
+    </row>
+    <row r="648" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A648" s="2"/>
+    </row>
+    <row r="649" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A649" s="2"/>
+    </row>
+    <row r="650" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A650" s="2"/>
+    </row>
+    <row r="651" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A651" s="2"/>
+    </row>
+    <row r="652" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A652" s="2"/>
+    </row>
+    <row r="653" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A653" s="2"/>
+    </row>
+    <row r="654" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A654" s="2"/>
+    </row>
+    <row r="655" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A655" s="2"/>
+    </row>
+    <row r="656" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A656" s="2"/>
+    </row>
+    <row r="657" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A657" s="2"/>
+    </row>
+    <row r="658" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A658" s="2"/>
+    </row>
+    <row r="659" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A659" s="2"/>
+    </row>
+    <row r="660" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A660" s="2"/>
+    </row>
+    <row r="661" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A661" s="2"/>
+    </row>
+    <row r="662" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A662" s="2"/>
+    </row>
+    <row r="663" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A663" s="2"/>
+    </row>
+    <row r="664" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A664" s="2"/>
+    </row>
+    <row r="665" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A665" s="2"/>
+    </row>
+    <row r="666" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A666" s="2"/>
+    </row>
+    <row r="667" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A667" s="2"/>
+    </row>
+    <row r="668" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A668" s="2"/>
+    </row>
+    <row r="669" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A669" s="2"/>
+    </row>
+    <row r="670" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A670" s="2"/>
+    </row>
+    <row r="671" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A671" s="2"/>
+    </row>
+    <row r="672" spans="1:1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="D1:D1000" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Geología"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="D1:D1000" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
